--- a/ai-adoption-opportunity-project/data/processed/benchmarks.xlsx
+++ b/ai-adoption-opportunity-project/data/processed/benchmarks.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26327"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d152c42fb0787e8e/IronHack/Projects/Project5/ai-adoption-opportunity-project/data/processed/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_F766B041513A94DD751F73523199A5087074CE80" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{486CAE28-6E35-415F-A467-FD16DB888908}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -28,9 +34,6 @@
     <t>scenario</t>
   </si>
   <si>
-    <t>value</t>
-  </si>
-  <si>
     <t>unit</t>
   </si>
   <si>
@@ -401,13 +404,16 @@
   </si>
   <si>
     <t>Midpoint of 30-75% for 2-3% cost reduction</t>
+  </si>
+  <si>
+    <t>kpi_value</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -444,6 +450,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -490,7 +504,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -522,9 +536,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -556,6 +588,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -731,11 +781,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I46"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -749,1324 +799,1324 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E2">
         <v>12.88</v>
       </c>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H2">
         <v>2025</v>
       </c>
       <c r="I2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E3">
-        <v>19.83</v>
+        <v>19.829999999999998</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H3">
         <v>2025</v>
       </c>
       <c r="I3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E4">
         <v>2.78</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H4">
         <v>2025</v>
       </c>
       <c r="I4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E5">
         <v>2.36</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H5">
         <v>2025</v>
       </c>
       <c r="I5" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E6">
-        <v>17.4</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="F6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H6">
         <v>2025</v>
       </c>
       <c r="I6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E7">
         <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H7">
         <v>2025</v>
       </c>
       <c r="I7" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E8">
         <v>0.5</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H8">
         <v>2025</v>
       </c>
       <c r="I8" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E9">
         <v>11.5</v>
       </c>
       <c r="F9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H9">
         <v>2025</v>
       </c>
       <c r="I9" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E10">
         <v>0.5</v>
       </c>
       <c r="F10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H10">
         <v>2025</v>
       </c>
       <c r="I10" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E11">
         <v>88.5</v>
       </c>
       <c r="F11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H11">
         <v>2025</v>
       </c>
       <c r="I11" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E12">
         <v>99.25</v>
       </c>
       <c r="F12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H12">
         <v>2025</v>
       </c>
       <c r="I12" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E13">
         <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H13">
         <v>2025</v>
       </c>
       <c r="I13" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E14">
         <v>30</v>
       </c>
       <c r="F14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H14">
         <v>2025</v>
       </c>
       <c r="I14" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E15">
         <v>80</v>
       </c>
       <c r="F15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H15">
         <v>2025</v>
       </c>
       <c r="I15" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E16">
         <v>65</v>
       </c>
       <c r="F16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H16">
         <v>2025</v>
       </c>
       <c r="I16" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E17">
         <v>42</v>
       </c>
       <c r="F17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H17">
         <v>2025</v>
       </c>
       <c r="I17" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E18">
         <v>99.5</v>
       </c>
       <c r="F18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G18" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H18">
         <v>2025</v>
       </c>
       <c r="I18" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E19">
         <v>30</v>
       </c>
       <c r="F19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H19">
         <v>2025</v>
       </c>
       <c r="I19" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E20">
         <v>85</v>
       </c>
       <c r="F20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G20" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H20">
         <v>2026</v>
       </c>
       <c r="I20" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E21">
         <v>99</v>
       </c>
       <c r="F21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H21">
         <v>2025</v>
       </c>
       <c r="I21" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E22">
         <v>36</v>
       </c>
       <c r="F22" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G22" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H22">
         <v>2025</v>
       </c>
       <c r="I22" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E23">
         <v>70</v>
       </c>
       <c r="F23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G23" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H23">
         <v>2026</v>
       </c>
       <c r="I23" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D24" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E24">
         <v>420</v>
       </c>
       <c r="F24" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G24" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H24">
         <v>2025</v>
       </c>
       <c r="I24" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E25">
         <v>30</v>
       </c>
       <c r="F25" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G25" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H25">
         <v>2025</v>
       </c>
       <c r="I25" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D26" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E26">
         <v>140</v>
       </c>
       <c r="F26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H26">
         <v>2025</v>
       </c>
       <c r="I26" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E27">
         <v>20</v>
       </c>
       <c r="F27" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G27" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H27">
         <v>2025</v>
       </c>
       <c r="I27" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D28" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E28">
         <v>105</v>
       </c>
       <c r="F28" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G28" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H28">
         <v>2025</v>
       </c>
       <c r="I28" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D29" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E29">
         <v>80</v>
       </c>
       <c r="F29" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G29" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H29">
         <v>2025</v>
       </c>
       <c r="I29" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D30" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E30">
         <v>45</v>
       </c>
       <c r="F30" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H30">
         <v>2025</v>
       </c>
       <c r="I30" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E31">
         <v>12</v>
       </c>
       <c r="F31" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G31" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H31">
         <v>2025</v>
       </c>
       <c r="I31" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C32" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D32" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E32">
         <v>78</v>
       </c>
       <c r="F32" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G32" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H32">
         <v>2025</v>
       </c>
       <c r="I32" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C33" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D33" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E33">
         <v>50</v>
       </c>
       <c r="F33" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G33" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H33">
         <v>2025</v>
       </c>
       <c r="I33" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C34" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E34">
         <v>878000</v>
       </c>
       <c r="F34" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G34" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H34">
         <v>2025</v>
       </c>
       <c r="I34" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C35" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D35" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E35">
         <v>70</v>
       </c>
       <c r="F35" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G35" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H35">
         <v>2025</v>
       </c>
       <c r="I35" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C36" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D36" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E36">
         <v>28</v>
       </c>
       <c r="F36" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G36" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H36">
         <v>2025</v>
       </c>
       <c r="I36" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C37" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D37" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E37">
         <v>72</v>
       </c>
       <c r="F37" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G37" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H37">
         <v>2026</v>
       </c>
       <c r="I37" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C38" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D38" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E38">
-        <v>2.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="F38" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G38" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H38">
         <v>2024</v>
       </c>
       <c r="I38" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C39" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D39" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E39">
         <v>50</v>
       </c>
       <c r="F39" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G39" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H39">
         <v>2025</v>
       </c>
       <c r="I39" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D40" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E40">
         <v>32.5</v>
       </c>
       <c r="F40" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G40" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H40">
         <v>2025</v>
       </c>
       <c r="I40" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C41" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D41" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E41">
         <v>60</v>
       </c>
       <c r="F41" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G41" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H41">
         <v>2025</v>
       </c>
       <c r="I41" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C42" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D42" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E42">
         <v>15</v>
       </c>
       <c r="F42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G42" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H42">
         <v>2025</v>
       </c>
       <c r="I42" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C43" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D43" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E43">
         <v>35</v>
       </c>
       <c r="F43" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G43" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H43">
         <v>2025</v>
       </c>
       <c r="I43" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C44" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D44" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E44">
         <v>65</v>
       </c>
       <c r="F44" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G44" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H44">
         <v>2025</v>
       </c>
       <c r="I44" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C45" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D45" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E45">
         <v>35</v>
       </c>
       <c r="F45" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G45" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H45">
         <v>2025</v>
       </c>
       <c r="I45" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C46" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D46" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E46">
         <v>52.5</v>
       </c>
       <c r="F46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G46" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H46">
         <v>2025</v>
       </c>
       <c r="I46" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
